--- a/data/trans_camb/IP16B01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B01-Clase-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,11; 94,67</t>
+          <t>53,25; 94,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66,22; 100,0</t>
+          <t>67,4; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,72; 93,42</t>
+          <t>48,93; 93,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,92; 94,82</t>
+          <t>68,66; 94,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,09; 96,32</t>
+          <t>68,45; 96,32</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,43; 88,17</t>
+          <t>49,34; 88,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,02; 88,99</t>
+          <t>27,42; 88,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72,31; 100,0</t>
+          <t>71,84; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,79; 93,05</t>
+          <t>67,38; 92,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,61; 93,36</t>
+          <t>65,32; 92,97</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>210,15; —</t>
+          <t>219,07; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>201,53; —</t>
+          <t>124,6; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>609,32; —</t>
+          <t>559,43; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>559,88; —</t>
+          <t>619,23; —</t>
         </is>
       </c>
     </row>
@@ -948,27 +948,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,49; 100,0</t>
+          <t>39,24; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,42; 100,0</t>
+          <t>68,04; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,51; 100,0</t>
+          <t>37,64; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,1; 100,0</t>
+          <t>76,76; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,21; 94,29</t>
+          <t>50,83; 93,97</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61,86; 87,62</t>
+          <t>60,7; 87,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70,79; 93,72</t>
+          <t>69,78; 93,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85,36; 100,0</t>
+          <t>86,76; 100,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61,76; 95,55</t>
+          <t>58,53; 95,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,97; 93,0</t>
+          <t>79,0; 92,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,05; 91,13</t>
+          <t>72,82; 91,48</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>67,34; 96,23</t>
+          <t>65,16; 96,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56,02; 90,61</t>
+          <t>54,07; 90,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74,55; 100,0</t>
+          <t>75,73; 100,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69,0; 100,0</t>
+          <t>68,18; 100,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>77,69; 94,69</t>
+          <t>77,38; 95,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68,94; 92,23</t>
+          <t>67,55; 92,67</t>
         </is>
       </c>
     </row>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>43,76; 100,0</t>
+          <t>43,51; 100,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>37,12; 92,17</t>
+          <t>35,53; 91,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66,95; 100,0</t>
+          <t>66,54; 100,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>68,93; 100,0</t>
+          <t>69,83; 100,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,82; 94,39</t>
+          <t>53,5; 94,41</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>73,46; 87,22</t>
+          <t>73,24; 87,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>70,55; 86,67</t>
+          <t>71,11; 86,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>87,48; 96,97</t>
+          <t>87,85; 96,8</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>79,21; 93,32</t>
+          <t>79,38; 93,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>83,05; 91,31</t>
+          <t>83,36; 91,3</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,42; 87,9</t>
+          <t>77,54; 88,36</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>1860,82; —</t>
+          <t>1987,14; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1656,09; —</t>
+          <t>1695,28; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4903,05; —</t>
+          <t>5002,1; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4147,58; —</t>
+          <t>4495,68; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B01-Clase-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,25; 94,65</t>
+          <t>54,62; 94,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,4; 100,0</t>
+          <t>63,8; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,93; 93,36</t>
+          <t>48,84; 93,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,66; 94,03</t>
+          <t>71,11; 94,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,45; 96,32</t>
+          <t>71,0; 100,0</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,34; 88,17</t>
+          <t>52,8; 88,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,42; 88,7</t>
+          <t>35,51; 89,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,84; 100,0</t>
+          <t>73,1; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,38; 92,66</t>
+          <t>67,48; 93,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,32; 92,97</t>
+          <t>64,64; 93,35</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>219,07; —</t>
+          <t>247,2; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>124,6; —</t>
+          <t>155,54; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>559,43; —</t>
+          <t>601,64; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>619,23; —</t>
+          <t>632,71; —</t>
         </is>
       </c>
     </row>
@@ -948,27 +948,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,24; 100,0</t>
+          <t>42,42; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,04; 100,0</t>
+          <t>67,09; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,64; 100,0</t>
+          <t>40,34; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>76,76; 100,0</t>
+          <t>79,66; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,83; 93,97</t>
+          <t>53,44; 93,97</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>60,7; 87,45</t>
+          <t>61,26; 87,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,78; 93,89</t>
+          <t>70,24; 93,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,76; 100,0</t>
+          <t>85,86; 100,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58,53; 95,32</t>
+          <t>60,24; 95,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,0; 92,71</t>
+          <t>78,73; 93,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,82; 91,48</t>
+          <t>72,07; 91,65</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>65,16; 96,19</t>
+          <t>67,22; 96,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54,07; 90,91</t>
+          <t>55,15; 90,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75,73; 100,0</t>
+          <t>75,52; 100,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68,18; 100,0</t>
+          <t>69,39; 100,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>77,38; 95,73</t>
+          <t>77,32; 95,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,55; 92,67</t>
+          <t>71,05; 93,32</t>
         </is>
       </c>
     </row>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>43,51; 100,0</t>
+          <t>41,63; 100,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35,53; 91,92</t>
+          <t>35,54; 91,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66,54; 100,0</t>
+          <t>60,11; 100,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>69,83; 100,0</t>
+          <t>70,02; 100,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,5; 94,41</t>
+          <t>56,1; 94,46</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>73,24; 87,27</t>
+          <t>73,86; 87,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>71,11; 86,64</t>
+          <t>71,16; 85,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>87,85; 96,8</t>
+          <t>87,94; 97,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>79,38; 93,4</t>
+          <t>79,11; 92,72</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>83,36; 91,3</t>
+          <t>83,48; 91,34</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>77,54; 88,36</t>
+          <t>77,73; 88,13</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>1987,14; —</t>
+          <t>1770,14; —</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1695,28; —</t>
+          <t>1692,06; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5002,1; —</t>
+          <t>4642,39; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4495,68; —</t>
+          <t>4528,21; —</t>
         </is>
       </c>
     </row>
